--- a/picks.xlsx
+++ b/picks.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -473,6 +473,8 @@
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,7 +510,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Goal (+5%)</t>
+          <t>Min Goal (+5%)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -609,6 +611,16 @@
       <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Engine</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>Chance +15%</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Earnings Before Deadline</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1292,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1316,7 +1327,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1359,7 +1369,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -1374,7 +1383,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1557,7 +1565,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -1579,7 +1586,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>

--- a/picks.xlsx
+++ b/picks.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -475,6 +475,7 @@
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="11" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -623,6 +624,11 @@
           <t>Earnings Before Deadline</t>
         </is>
       </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Sell Signal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -708,14 +714,28 @@
           <t>OPEN</t>
         </is>
       </c>
+      <c r="V2" t="n">
+        <v>159.64</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-2.4</v>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>v1</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>hold — ordinary stops tested worse; sell only on a close at/below $139.51 (-15% disaster stop), else at the deadline 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -801,14 +821,28 @@
           <t>OPEN</t>
         </is>
       </c>
+      <c r="V3" t="n">
+        <v>1162.84</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>v1</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>hold — ordinary stops tested worse; sell only on a close at/below $987.73 (-15% disaster stop), else at the deadline 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -894,14 +928,28 @@
           <t>OPEN</t>
         </is>
       </c>
+      <c r="V4" t="n">
+        <v>91.34</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-1.2</v>
+      </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>v1</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>hold — ordinary stops tested worse; sell only on a close at/below $79.17 (-15% disaster stop), else at the deadline 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1054,9 @@
       <c r="A7" t="n">
         <v>3.2</v>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>-1.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1071,7 +1121,9 @@
       <c r="F11" t="n">
         <v>3.2</v>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>-1.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1136,7 +1188,9 @@
       <c r="F15" t="n">
         <v>3.2</v>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>-1.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1201,7 +1255,9 @@
       <c r="F19" t="n">
         <v>3.2</v>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>-1.5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1266,7 +1322,9 @@
       <c r="F23" t="n">
         <v>3.2</v>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>-1.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/picks.xlsx
+++ b/picks.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -476,6 +476,7 @@
     <col width="11" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -629,6 +630,11 @@
           <t>Sell Signal</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Sell Below (Disaster)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -735,7 +741,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>hold — ordinary stops tested worse; sell only on a close at/below $139.51 (-15% disaster stop), else at the deadline 2026-10-02</t>
+          <t>hold — ordinary stops tested worse; sell only on a close at/below $139.51 (this stock's own disaster level), else at the deadline 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -842,7 +848,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>hold — ordinary stops tested worse; sell only on a close at/below $987.73 (-15% disaster stop), else at the deadline 2026-10-02</t>
+          <t>hold — ordinary stops tested worse; sell only on a close at/below $987.73 (this stock's own disaster level), else at the deadline 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -949,7 +955,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>hold — ordinary stops tested worse; sell only on a close at/below $79.17 (-15% disaster stop), else at the deadline 2026-10-02</t>
+          <t>hold — ordinary stops tested worse; sell only on a close at/below $79.17 (this stock's own disaster level), else at the deadline 2026-10-02</t>
         </is>
       </c>
     </row>

--- a/picks.xlsx
+++ b/picks.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Picks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Track Record" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="How To Read This" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Track Record" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Read This" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE4"/>
+  <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -477,6 +477,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,6 +634,11 @@
       <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Sell Below (Disaster)</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Segment</t>
         </is>
       </c>
     </row>

--- a/picks.xlsx
+++ b/picks.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
@@ -65,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -78,6 +82,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -478,6 +483,7 @@
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="11" customWidth="1" min="31" max="31"/>
     <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -639,6 +645,11 @@
       <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Segment</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ML Check</t>
         </is>
       </c>
     </row>
@@ -1349,336 +1360,710 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>How to read this scorecard</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>HOW TO BUY (tested rule — read this first):</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Buy at or near the market CLOSE — never at the open,</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Every time the scout runs, it adds its picks here and re-checks the old ones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A pick is a HIT if the stock's closing price gained 5% or more at any point</t>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>and never chase a morning gap up.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>before the Deadline (about 2 months). After the Deadline, it's a MISS.</t>
+          <t>How to read this scorecard</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5% is the minimum goal — the gain columns show how much further these</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>stocks usually go.</t>
+          <t>Every time the scout runs, it adds its picks here and re-checks the old ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A pick is a HIT if the stock's closing price gained 5% or more at any point</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>There are two lists:</t>
+          <t>before the Deadline (about 2 months). After the Deadline, it's a MISS.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>- "Best Overall": the best balance of chance, size of gain, speed and safety.</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>- "Biggest Gain": the biggest expected gains, but only stocks with at least</t>
+          <t>IMPORTANT: 5% is the MINIMUM bar, not the goal. The tool ranks picks by how</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  a 62% chance of reaching +5%. Some runs this list is short or empty —</t>
+          <t>far and how fast they usually run (see Usual Peak %, Chance +10%, Chance</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  that means nothing honest qualified, not that the tool forgot.</t>
+          <t>+15%), and a pick that HITs keeps being re-priced until its Deadline — so</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- "Both" means the stock made both lists.</t>
+          <t>"Best So Far %" shows how far the winner actually ran, not just that it</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cleared the bar.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>What the prediction columns mean (all measured from 10 years of stocks that</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>looked the same — same pattern, same energy level, same market mood):</t>
+          <t>There are two lists:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>- "Best Overall": the best balance of chance, size of gain, speed and safety.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chance +5%        How often such stocks gained at least 5% within 2 months.</t>
+          <t>- "Biggest Gain": the biggest expected gains, but only stocks with at least</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chance +10%       How often they gained at least 10%.</t>
+          <t xml:space="preserve">  a 62% chance of reaching +5%. Some runs this list is short or empty —</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Usual Gain %      Where they typically ENDED after 2 months (often below 5 —</t>
+          <t xml:space="preserve">  that means nothing honest qualified, not that the tool forgot.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  that's the honest truth, not a mistake).</t>
+          <t>- "Both" means the stock made both lists.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Usual Peak %      The best gain they typically reached at some point.</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Analysts' Guess % (corrected)  What Wall Street analysts' price targets say</t>
+          <t>What the prediction columns mean (all measured from 10 years of stocks that</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  the stock will do over ONE YEAR — after correcting their</t>
+          <t>looked the same — same pattern, same energy level, same market mood):</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                  well-documented over-optimism. Analysts overshoot by about</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  7-12 points on average, so we shrink their claim:</t>
+          <t>Chance +5%        How often such stocks gained at least 5% within 2 months.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  corrected = 5% + 0.22 x their claimed gain. "n/r" means</t>
+          <t>Chance +10%       How often they gained at least 10%.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  their targets disagree so widely (or are so stale) that the</t>
+          <t>Chance +15%       How often they gained at least 15%.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  number isn't reliable — research shows widely-scattered</t>
+          <t>Usual Gain %      Where they typically ENDED after 2 months (often below 5 —</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  targets actually predict BADLY. Note this is a 1-YEAR view</t>
+          <t xml:space="preserve">                  that's the honest truth, not a mistake).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  shown for context; the pick itself is a 2-month idea chosen</t>
+          <t>Usual Peak %      The best gain they typically reached at some point (the</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  from history, and a giant claimed upside is a warning sign,</t>
+          <t xml:space="preserve">                  ranking uses the AVERAGE peak, which gives extra credit to</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  not a promise.</t>
+          <t xml:space="preserve">                  groups with big winners — because 5% is only the minimum).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Usual Days to +5% How many trading days it usually took to reach +5%.</t>
+          <t>Analysts' Guess % (corrected)  What Wall Street analysts' price targets say</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Chance of -5% Dip First  How often they fell 5% before rising 5%. Important!</t>
+          <t xml:space="preserve">                  the stock will do over ONE YEAR — after correcting their</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Avg Stock Chance +5%     How often ANY normal S&amp;P stock reached +5% in the</t>
+          <t xml:space="preserve">                  well-documented over-optimism. Analysts overshoot by about</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  same kind of market. In good times most do — a pick is only</t>
+          <t xml:space="preserve">                  7-12 points on average, so we shrink their claim:</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  special if its chance beats this number.</t>
+          <t xml:space="preserve">                  corrected = 5% + 0.22 x their claimed gain. "n/r" means</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Overall Score     Chance x size of gain x speed x safety, in one number.</t>
+          <t xml:space="preserve">                  their targets disagree so widely (or are so stale) that the</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  Higher = better. Only compare within the same run.</t>
+          <t xml:space="preserve">                  number isn't reliable — research shows widely-scattered</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gain Score        Usual peak x chance of +10% — the "how big" ranking.</t>
+          <t xml:space="preserve">                  targets actually predict BADLY. Note this is a 1-YEAR view</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Confidence        A = proven edge over the average stock. B = modest edge.</t>
+          <t xml:space="preserve">                  shown for context; the pick itself is a 2-month idea chosen</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  C = no proven edge (kept only if something else is special).</t>
+          <t xml:space="preserve">                  from history, and a giant claimed upside is a warning sign,</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  not a promise.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>What-happened columns:</t>
+          <t>Usual Days to +5% How many trading days it usually took to reach +5%.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Gain So Far %     Where the stock is now vs the pick price.</t>
+          <t>Chance of -5% Dip First  How often they fell 5% before rising 5%. Important!</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Best So Far %     The best it has reached since picked — shows near-misses.</t>
+          <t>Avg Stock Chance +5%     How often ANY normal S&amp;P stock reached +5% in the</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  same kind of market. In good times most do — a pick is only</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Honesty notes: numbers come from 2016-2026 — mostly good years for stocks;</t>
+          <t xml:space="preserve">                  special if its chance beats this number.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>the tool refuses to give numbers when history is too thin; reaching +5% at</t>
+          <t>Overall Score     Chance x size of gain x speed x safety, in one number.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>some point is NOT the same as ending with a profit. This is a research</t>
+          <t xml:space="preserve">                  Higher = better. Only compare within the same run.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
+        <is>
+          <t>Gain Score        Usual peak x chance of +10% — the "how big" ranking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Confidence        A = proven edge over the average stock. B = modest edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  C = no proven edge (kept only if something else is special).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Engine            Which version of the scanner chose the pick (v1, v3...).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  Versions are scored separately in the Track Record so an</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  upgrade can't hide behind the old version's results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Earnings Before Deadline  The company's next quarterly report date, if it</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  lands before the Deadline. Know the date — a report can</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  wreck a single pick overnight — but on real SEC data,</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  picks WITH a report ahead in their window were the</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  BETTER group (the report is the fuel for the +5% move).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  What the tool avoids instead is stocks that JUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  reported: with the report behind them they reached +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  only ~40-47% of the time vs ~62% normally, so they get</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  pushed down the lists automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sell Signal       When to sell, updated every run — and specific to EACH</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  stock, not one wide rule. Ten years of testing say</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  ordinary stop-losses make results WORSE (stocks dip and</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  recover too often, and crashes gap right through stops).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  The rules that survived testing:</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  1) Disaster stop, sized to the stock: if it closes below</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                     "Sell Below (Disaster)" — 2x that stock's own normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                     2-month move under the buy price — sell; the pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                     is broken. A calm stock gets a tighter level, a lively</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                     one gets more room. Rarely fires; caps catastrophes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  2) Otherwise no stop — sell at the Deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  3) Once it has touched +5%, never let it become a loss:</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                     sell on any close back at/below your buy price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                     (A tighter "8% below its peak" version was tested and</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                     sold winners that kept running — rejected.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  This column shows the live instruction with exact price</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  levels. Protection buys smaller losses, not bigger gains</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  (roughly free if you re-invest the freed cash).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sell Below (Disaster)  This stock's own disaster price, computed on the day</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  it was picked from how much it normally moves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>What-happened columns:</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Gain So Far %     Where the stock is now vs the pick price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Best So Far %     The best it has reached since picked — shows near-misses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Segment           Where the stock lives: large (S&amp;P 500), mid (400) or</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  small (600) — mid/small are the under-the-radar names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ML Check          The tool's own second opinion: a small model trained on</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  the tool's OWN past picks estimates this pick's chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  of hitting +5%, from patterns the ranking alone misses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  "strong" picks historically hit 73% (avg +4.4%);</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  "weak" ones 55% (avg ~0%). Treat "weak" as a red flag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  Computed only when you run the tool — nothing runs in</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  the background.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Honesty notes: numbers come from 2016-2026 — mostly good years for stocks;</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>the tool refuses to give numbers when history is too thin; reaching +5% at</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>some point is NOT the same as ending with a profit. This is a research</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>scorecard, NOT financial advice. Nothing is ever bought automatically.</t>
         </is>

--- a/picks.xlsx
+++ b/picks.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>ML Check</t>
+          <t>Insider Buys</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A106"/>
+  <dimension ref="A1:A108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,78 +1992,92 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ML Check          The tool's own second opinion: a small model trained on</t>
+          <t>Insider Buys      Filled when company officers or directors bought their</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  the tool's OWN past picks estimates this pick's chance</t>
+          <t xml:space="preserve">                  OWN stock on the open market in the 45 days before the</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  of hitting +5%, from patterns the ranking alone misses.</t>
+          <t xml:space="preserve">                  pick (real SEC filings, checked at scan time). Rare on</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  "strong" picks historically hit 73% (avg +4.4%);</t>
+          <t xml:space="preserve">                  momentum names — and historically excellent when it</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  "weak" ones 55% (avg ~0%). Treat "weak" as a red flag.</t>
+          <t xml:space="preserve">                  happens (in our sample such picks hit 69% with +6.9%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  Computed only when you run the tool — nothing runs in</t>
+          <t xml:space="preserve">                  average and zero disasters, though the sample is small).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  the background.</t>
+          <t xml:space="preserve">                  A plus to note, never a guarantee. Insider SELLING is</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  deliberately ignored — heavy selling into strength</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Honesty notes: numbers come from 2016-2026 — mostly good years for stocks;</t>
+          <t xml:space="preserve">                  tested as profit-taking noise, not a warning.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>the tool refuses to give numbers when history is too thin; reaching +5% at</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>some point is NOT the same as ending with a profit. This is a research</t>
+          <t>Honesty notes: numbers come from 2016-2026 — mostly good years for stocks;</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
+        <is>
+          <t>the tool refuses to give numbers when history is too thin; reaching +5% at</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>some point is NOT the same as ending with a profit. This is a research</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>scorecard, NOT financial advice. Nothing is ever bought automatically.</t>
         </is>

--- a/picks.xlsx
+++ b/picks.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="1" r:id="Rdc210d98d1c74c8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Track Record" sheetId="2" r:id="R1d9541f815ad464e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Read This" sheetId="3" r:id="R6dab8729227540b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Status" sheetId="4" r:id="R1506efc22b4e48dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="1" r:id="Rf1c92a74b0a74060"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Track Record" sheetId="2" r:id="R4bff5232c2b843b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Read This" sheetId="3" r:id="R8cc0b2fa22a4455d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Status" sheetId="4" r:id="Rfee08e634413478d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4691,7 +4691,9 @@
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="89" t="str"/>
+      <x:c r="A17" s="89" t="str">
+        <x:v>Track a frozen candidate for at least six months; twelve months is the default, and a longer written gate wins.</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="93" t="str">
